--- a/test-data/orange-test-data.xlsx
+++ b/test-data/orange-test-data.xlsx
@@ -7,6 +7,7 @@
     <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="validLoginTest" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Sheet4" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="addValidEmployeeTest" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>Username</t>
   </si>
@@ -50,6 +51,42 @@
   </si>
   <si>
     <t>Quick Launch</t>
+  </si>
+  <si>
+    <t>firstname</t>
+  </si>
+  <si>
+    <t>middlename</t>
+  </si>
+  <si>
+    <t>lastname</t>
+  </si>
+  <si>
+    <t>expectedValue</t>
+  </si>
+  <si>
+    <t>jack</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>wick</t>
+  </si>
+  <si>
+    <t>jack wick</t>
+  </si>
+  <si>
+    <t>jack2</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>wick2</t>
+  </si>
+  <si>
+    <t>jack2 wick2</t>
   </si>
 </sst>
 </file>
@@ -111,6 +148,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -410,4 +451,76 @@
   <sheetData/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>